--- a/output/2026-09-02/enriched_analysis.xlsx
+++ b/output/2026-09-02/enriched_analysis.xlsx
@@ -616,7 +616,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
+          <t>Gandhar Oil Refinery (India) Limited</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>Ganesh Consumer Products Limited</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -5217,7 +5217,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GANDHAR OIL REFINERY (INDIA) LIMITED</t>
+          <t>Gandhar Oil Refinery (India) Limited</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6267,7 +6267,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GANESH CONSUMER PRODUCTS LIMITED</t>
+          <t>Ganesh Consumer Products Limited</t>
         </is>
       </c>
       <c r="C32" t="n">

--- a/output/2026-09-02/enriched_analysis.xlsx
+++ b/output/2026-09-02/enriched_analysis.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC48"/>
+  <dimension ref="A1:AC47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -663,13 +663,13 @@
         </is>
       </c>
       <c r="P2" t="n">
-        <v>0.077</v>
+        <v>0.076</v>
       </c>
       <c r="Q2" t="n">
-        <v>2601</v>
+        <v>2628</v>
       </c>
       <c r="R2" t="n">
-        <v>8.94</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="S2" t="n">
         <v>36</v>
@@ -740,19 +740,19 @@
         <v>89.79000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>55.78</v>
+        <v>56.48</v>
       </c>
       <c r="K3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L3" t="n">
         <v>67.45999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>6.19</v>
+        <v>3.94</v>
       </c>
       <c r="N3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -760,13 +760,13 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>0.66</v>
+        <v>0.411</v>
       </c>
       <c r="Q3" t="n">
-        <v>938</v>
+        <v>958</v>
       </c>
       <c r="R3" t="n">
-        <v>26.8</v>
+        <v>27.4</v>
       </c>
       <c r="S3" t="n">
         <v>19</v>
@@ -805,12 +805,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -834,80 +834,80 @@
         <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>826.9</v>
+        <v>276.35</v>
       </c>
       <c r="J4" t="n">
-        <v>746.02</v>
+        <v>217.8</v>
       </c>
       <c r="K4" t="n">
-        <v>10.8</v>
+        <v>26.9</v>
       </c>
       <c r="L4" t="n">
-        <v>69.61</v>
+        <v>71.75</v>
       </c>
       <c r="M4" t="n">
-        <v>7.69</v>
+        <v>0.82</v>
       </c>
       <c r="N4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0.047</v>
+        <v>0.065</v>
       </c>
       <c r="Q4" t="n">
-        <v>16245</v>
+        <v>1260</v>
       </c>
       <c r="R4" t="n">
-        <v>20.6</v>
+        <v>17</v>
       </c>
       <c r="S4" t="n">
-        <v>16</v>
+        <v>55</v>
       </c>
       <c r="T4" t="n">
-        <v>346</v>
+        <v>40</v>
       </c>
       <c r="U4" t="n">
-        <v>88</v>
+        <v>54</v>
       </c>
       <c r="V4" t="n">
-        <v>10.02</v>
+        <v>8.23</v>
       </c>
       <c r="W4" t="n">
-        <v>12.3</v>
+        <v>11</v>
       </c>
       <c r="X4" t="n">
-        <v>0.21</v>
+        <v>0.01</v>
       </c>
       <c r="Y4" t="b">
         <v>1</v>
       </c>
       <c r="Z4" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="AA4" t="n">
-        <v>820.4</v>
+        <v>215.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>791.04</v>
+        <v>181.7</v>
       </c>
       <c r="AC4" t="n">
-        <v>13.3</v>
+        <v>79.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -931,69 +931,69 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>276.35</v>
+        <v>826.9</v>
       </c>
       <c r="J5" t="n">
-        <v>217.8</v>
+        <v>746.02</v>
       </c>
       <c r="K5" t="n">
-        <v>26.9</v>
+        <v>10.8</v>
       </c>
       <c r="L5" t="n">
-        <v>71.75</v>
+        <v>69.61</v>
       </c>
       <c r="M5" t="n">
-        <v>0.82</v>
+        <v>7.69</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0.068</v>
+        <v>0.048</v>
       </c>
       <c r="Q5" t="n">
-        <v>1212</v>
+        <v>16001</v>
       </c>
       <c r="R5" t="n">
-        <v>16.3</v>
+        <v>20.2</v>
       </c>
       <c r="S5" t="n">
-        <v>55</v>
+        <v>16</v>
       </c>
       <c r="T5" t="n">
-        <v>40</v>
+        <v>346</v>
       </c>
       <c r="U5" t="n">
-        <v>54</v>
+        <v>88</v>
       </c>
       <c r="V5" t="n">
-        <v>8.23</v>
+        <v>10.02</v>
       </c>
       <c r="W5" t="n">
-        <v>11</v>
+        <v>12.3</v>
       </c>
       <c r="X5" t="n">
-        <v>0.01</v>
+        <v>0.21</v>
       </c>
       <c r="Y5" t="b">
         <v>1</v>
       </c>
       <c r="Z5" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="AA5" t="n">
-        <v>215.74</v>
+        <v>820.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>181.7</v>
+        <v>791.04</v>
       </c>
       <c r="AC5" t="n">
-        <v>79.7</v>
+        <v>13.3</v>
       </c>
     </row>
     <row r="6">
@@ -1051,13 +1051,13 @@
         </is>
       </c>
       <c r="P6" t="n">
-        <v>0.5</v>
+        <v>0.491</v>
       </c>
       <c r="Q6" t="n">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="R6" t="n">
-        <v>8.84</v>
+        <v>9.01</v>
       </c>
       <c r="S6" t="n">
         <v>17</v>
@@ -1151,10 +1151,10 @@
         <v>0.044</v>
       </c>
       <c r="Q7" t="n">
-        <v>16280</v>
+        <v>16374</v>
       </c>
       <c r="R7" t="n">
-        <v>41.4</v>
+        <v>41.7</v>
       </c>
       <c r="S7" t="n">
         <v>83</v>
@@ -1245,13 +1245,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0.156</v>
+        <v>0.158</v>
       </c>
       <c r="Q8" t="n">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="R8" t="n">
-        <v>59.5</v>
+        <v>58.8</v>
       </c>
       <c r="S8" t="n">
         <v>3</v>
@@ -1269,7 +1269,7 @@
         <v>11.6</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="b">
         <v>1</v>
@@ -1342,13 +1342,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0.485</v>
+        <v>0.486</v>
       </c>
       <c r="Q9" t="n">
-        <v>1652</v>
+        <v>1650</v>
       </c>
       <c r="R9" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="S9" t="n">
         <v>581</v>
@@ -1385,12 +1385,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="G10" t="n">
         <v>25</v>
@@ -1414,80 +1414,80 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>100.14</v>
+        <v>367.9</v>
       </c>
       <c r="J10" t="n">
-        <v>91.62</v>
+        <v>338.1</v>
       </c>
       <c r="K10" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>70.88</v>
+        <v>66.73</v>
       </c>
       <c r="M10" t="n">
-        <v>8.390000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="N10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>0.326</v>
+        <v>0.078</v>
       </c>
       <c r="Q10" t="n">
-        <v>2572</v>
+        <v>438</v>
       </c>
       <c r="R10" t="n">
-        <v>21.1</v>
+        <v>12.9</v>
       </c>
       <c r="S10" t="n">
-        <v>8</v>
+        <v>-8</v>
       </c>
       <c r="T10" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="U10" t="n">
-        <v>-14</v>
+        <v>33</v>
       </c>
       <c r="V10" t="n">
-        <v>0.57</v>
+        <v>14.36</v>
       </c>
       <c r="W10" t="n">
-        <v>16.9</v>
+        <v>9.94</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01</v>
+        <v>0.23</v>
       </c>
       <c r="Y10" t="b">
         <v>1</v>
       </c>
       <c r="Z10" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>90.77</v>
+        <v>323.51</v>
       </c>
       <c r="AB10" t="n">
-        <v>91.98999999999999</v>
+        <v>260.65</v>
       </c>
       <c r="AC10" t="n">
-        <v>9.9</v>
+        <v>70.90000000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F11" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G11" t="n">
         <v>25</v>
@@ -1511,80 +1511,78 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>367.9</v>
+        <v>193.17</v>
       </c>
       <c r="J11" t="n">
-        <v>338.1</v>
+        <v>164.1</v>
       </c>
       <c r="K11" t="n">
-        <v>8.800000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="L11" t="n">
-        <v>66.73</v>
+        <v>60.6</v>
       </c>
       <c r="M11" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0.079</v>
+        <v>0.006</v>
       </c>
       <c r="Q11" t="n">
-        <v>432</v>
-      </c>
-      <c r="R11" t="n">
-        <v>12.8</v>
-      </c>
+        <v>4133</v>
+      </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-8</v>
+        <v>39</v>
       </c>
       <c r="T11" t="n">
-        <v>24</v>
+        <v>258</v>
       </c>
       <c r="U11" t="n">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="V11" t="n">
-        <v>14.36</v>
+        <v>-1.13</v>
       </c>
       <c r="W11" t="n">
-        <v>9.94</v>
+        <v>6.38</v>
       </c>
       <c r="X11" t="n">
-        <v>0.23</v>
+        <v>10.11</v>
       </c>
       <c r="Y11" t="b">
         <v>1</v>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>61</v>
       </c>
       <c r="AA11" t="n">
-        <v>323.51</v>
+        <v>178.32</v>
       </c>
       <c r="AB11" t="n">
-        <v>260.65</v>
+        <v>178.57</v>
       </c>
       <c r="AC11" t="n">
-        <v>70.90000000000001</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -1596,10 +1594,10 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="G12" t="n">
         <v>25</v>
@@ -1608,67 +1606,69 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>193.17</v>
+        <v>100.14</v>
       </c>
       <c r="J12" t="n">
-        <v>164.1</v>
+        <v>91.62</v>
       </c>
       <c r="K12" t="n">
-        <v>17.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>60.6</v>
+        <v>70.88</v>
       </c>
       <c r="M12" t="n">
-        <v>0.25</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="N12" t="n">
         <v>4</v>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0.006</v>
+        <v>0.293</v>
       </c>
       <c r="Q12" t="n">
-        <v>4117</v>
-      </c>
-      <c r="R12" t="inlineStr"/>
+        <v>2865</v>
+      </c>
+      <c r="R12" t="n">
+        <v>23.5</v>
+      </c>
       <c r="S12" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="T12" t="n">
-        <v>258</v>
+        <v>14</v>
       </c>
       <c r="U12" t="n">
-        <v>30</v>
+        <v>-14</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.13</v>
+        <v>0.57</v>
       </c>
       <c r="W12" t="n">
-        <v>6.38</v>
+        <v>16.9</v>
       </c>
       <c r="X12" t="n">
-        <v>10.11</v>
+        <v>0.01</v>
       </c>
       <c r="Y12" t="b">
         <v>1</v>
       </c>
       <c r="Z12" t="n">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="AA12" t="n">
-        <v>178.32</v>
+        <v>90.77</v>
       </c>
       <c r="AB12" t="n">
-        <v>178.57</v>
+        <v>91.98999999999999</v>
       </c>
       <c r="AC12" t="n">
-        <v>11</v>
+        <v>9.9</v>
       </c>
     </row>
     <row r="13">
@@ -1732,7 +1732,7 @@
         <v>318</v>
       </c>
       <c r="R13" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="S13" t="n">
         <v>22</v>
@@ -1771,16 +1771,16 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NUPUR RECYCLERS LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1791,89 +1791,89 @@
         <v>20</v>
       </c>
       <c r="F14" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G14" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="H14" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>122</v>
+        <v>82.67</v>
       </c>
       <c r="J14" t="n">
-        <v>82.93000000000001</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>47.1</v>
+        <v>7</v>
       </c>
       <c r="L14" t="n">
-        <v>72.53</v>
+        <v>62.78</v>
       </c>
       <c r="M14" t="n">
-        <v>0.42</v>
+        <v>2.77</v>
       </c>
       <c r="N14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0.05</v>
+        <v>0.652</v>
       </c>
       <c r="Q14" t="n">
-        <v>843</v>
+        <v>425</v>
       </c>
       <c r="R14" t="n">
-        <v>90</v>
+        <v>39.4</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="T14" t="n">
-        <v>1.43</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>82</v>
+        <v>-19</v>
       </c>
       <c r="V14" t="n">
-        <v>0.34</v>
+        <v>1.54</v>
       </c>
       <c r="W14" t="n">
-        <v>9.710000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.28</v>
       </c>
       <c r="Y14" t="b">
         <v>1</v>
       </c>
       <c r="Z14" t="n">
-        <v>3.67</v>
+        <v>41.64</v>
       </c>
       <c r="AA14" t="n">
-        <v>107.79</v>
+        <v>75.97</v>
       </c>
       <c r="AB14" t="n">
-        <v>69.98</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="AC14" t="n">
-        <v>137.6</v>
+        <v>10.2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -1888,93 +1888,89 @@
         <v>20</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G15" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>82.67</v>
+        <v>19.3</v>
       </c>
       <c r="J15" t="n">
-        <v>77.26000000000001</v>
+        <v>21.01</v>
       </c>
       <c r="K15" t="n">
-        <v>7</v>
+        <v>-8.1</v>
       </c>
       <c r="L15" t="n">
-        <v>62.78</v>
+        <v>70.87</v>
       </c>
       <c r="M15" t="n">
-        <v>2.77</v>
+        <v>0.5</v>
       </c>
       <c r="N15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
       <c r="P15" t="n">
-        <v>0.652</v>
+        <v>0.132</v>
       </c>
       <c r="Q15" t="n">
-        <v>425</v>
+        <v>379</v>
       </c>
       <c r="R15" t="n">
-        <v>39.4</v>
+        <v>6.11</v>
       </c>
       <c r="S15" t="n">
-        <v>21</v>
-      </c>
-      <c r="T15" t="n">
-        <v>8.390000000000001</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
       <c r="U15" t="n">
-        <v>-19</v>
+        <v>391</v>
       </c>
       <c r="V15" t="n">
-        <v>1.54</v>
+        <v>1.03</v>
       </c>
       <c r="W15" t="n">
-        <v>8.73</v>
+        <v>18.5</v>
       </c>
       <c r="X15" t="n">
-        <v>0.28</v>
+        <v>0.01</v>
       </c>
       <c r="Y15" t="b">
-        <v>1</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>41.64</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="n">
-        <v>75.97</v>
+        <v>18.21</v>
       </c>
       <c r="AB15" t="n">
-        <v>78.26000000000001</v>
+        <v>15.13</v>
       </c>
       <c r="AC15" t="n">
-        <v>10.2</v>
+        <v>33.4</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1985,74 +1981,78 @@
         <v>20</v>
       </c>
       <c r="F16" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H16" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I16" t="n">
+        <v>601.45</v>
+      </c>
+      <c r="J16" t="n">
+        <v>580.77</v>
+      </c>
+      <c r="K16" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L16" t="n">
+        <v>64.68000000000001</v>
+      </c>
+      <c r="M16" t="n">
+        <v>6.04</v>
+      </c>
+      <c r="N16" t="n">
+        <v>44</v>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>31-08-2026</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0.539</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1120</v>
+      </c>
+      <c r="R16" t="n">
+        <v>57.1</v>
+      </c>
+      <c r="S16" t="n">
+        <v>21</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="U16" t="n">
+        <v>23</v>
+      </c>
+      <c r="V16" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="W16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="X16" t="n">
         <v>0</v>
-      </c>
-      <c r="I16" t="n">
-        <v>19.3</v>
-      </c>
-      <c r="J16" t="n">
-        <v>21.01</v>
-      </c>
-      <c r="K16" t="n">
-        <v>-8.1</v>
-      </c>
-      <c r="L16" t="n">
-        <v>70.87</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="N16" t="n">
-        <v>3</v>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>19-08-2026</t>
-        </is>
-      </c>
-      <c r="P16" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>366</v>
-      </c>
-      <c r="R16" t="n">
-        <v>5.92</v>
-      </c>
-      <c r="S16" t="n">
-        <v>118</v>
-      </c>
-      <c r="T16" t="inlineStr"/>
-      <c r="U16" t="n">
-        <v>391</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W16" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="X16" t="n">
-        <v>0.01</v>
       </c>
       <c r="Y16" t="b">
         <v>0</v>
       </c>
-      <c r="Z16" t="inlineStr"/>
+      <c r="Z16" t="n">
+        <v>-110</v>
+      </c>
       <c r="AA16" t="n">
-        <v>18.21</v>
+        <v>573.86</v>
       </c>
       <c r="AB16" t="n">
-        <v>15.13</v>
+        <v>507.73</v>
       </c>
       <c r="AC16" t="n">
-        <v>33.4</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="17">
@@ -2113,10 +2113,10 @@
         <v>0.007</v>
       </c>
       <c r="Q17" t="n">
-        <v>5712</v>
+        <v>5736</v>
       </c>
       <c r="R17" t="n">
-        <v>9.65</v>
+        <v>9.68</v>
       </c>
       <c r="S17" t="n">
         <v>43</v>
@@ -2155,16 +2155,16 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>Prataap Snacks Limited</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2172,96 +2172,96 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F18" t="n">
+        <v>21</v>
+      </c>
+      <c r="G18" t="n">
         <v>15</v>
       </c>
-      <c r="G18" t="n">
-        <v>25</v>
-      </c>
       <c r="H18" t="n">
-        <v>-2</v>
+        <v>-5</v>
       </c>
       <c r="I18" t="n">
-        <v>601.45</v>
+        <v>1155.2</v>
       </c>
       <c r="J18" t="n">
-        <v>580.77</v>
+        <v>1174.34</v>
       </c>
       <c r="K18" t="n">
-        <v>3.6</v>
+        <v>-1.6</v>
       </c>
       <c r="L18" t="n">
-        <v>64.68000000000001</v>
+        <v>69.75</v>
       </c>
       <c r="M18" t="n">
-        <v>6.04</v>
+        <v>65.58</v>
       </c>
       <c r="N18" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0.544</v>
+        <v>2.368</v>
       </c>
       <c r="Q18" t="n">
-        <v>1110</v>
+        <v>2769</v>
       </c>
       <c r="R18" t="n">
-        <v>56.5</v>
+        <v>217</v>
       </c>
       <c r="S18" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.11</v>
+        <v>19.05</v>
       </c>
       <c r="U18" t="n">
-        <v>23</v>
+        <v>194</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.07000000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.58</v>
+        <v>3.08</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="Y18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z18" t="n">
-        <v>-110</v>
+        <v>3.87</v>
       </c>
       <c r="AA18" t="n">
-        <v>573.86</v>
+        <v>1166.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>507.73</v>
+        <v>1085.58</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.1</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prataap Snacks Limited</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2269,96 +2269,96 @@
         </is>
       </c>
       <c r="E19" t="n">
+        <v>15</v>
+      </c>
+      <c r="F19" t="n">
+        <v>14</v>
+      </c>
+      <c r="G19" t="n">
         <v>25</v>
       </c>
-      <c r="F19" t="n">
-        <v>21</v>
-      </c>
-      <c r="G19" t="n">
-        <v>15</v>
-      </c>
       <c r="H19" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1155.2</v>
+        <v>498.2</v>
       </c>
       <c r="J19" t="n">
-        <v>1174.34</v>
+        <v>482.22</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.6</v>
+        <v>3.3</v>
       </c>
       <c r="L19" t="n">
-        <v>69.75</v>
+        <v>62.09</v>
       </c>
       <c r="M19" t="n">
-        <v>65.58</v>
+        <v>0.79</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2.38</v>
+        <v>0.091</v>
       </c>
       <c r="Q19" t="n">
-        <v>2755</v>
+        <v>869</v>
       </c>
       <c r="R19" t="n">
-        <v>216</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T19" t="n">
-        <v>19.05</v>
+        <v>30</v>
       </c>
       <c r="U19" t="n">
-        <v>194</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>14.66</v>
       </c>
       <c r="W19" t="n">
-        <v>3.08</v>
+        <v>14.4</v>
       </c>
       <c r="X19" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="Y19" t="b">
         <v>1</v>
       </c>
       <c r="Z19" t="n">
-        <v>3.87</v>
+        <v>14</v>
       </c>
       <c r="AA19" t="n">
-        <v>1166.07</v>
+        <v>489.28</v>
       </c>
       <c r="AB19" t="n">
-        <v>1085.58</v>
+        <v>488.46</v>
       </c>
       <c r="AC19" t="n">
-        <v>7.9</v>
+        <v>4.7</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F20" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G20" t="n">
         <v>25</v>
@@ -2378,80 +2378,80 @@
         <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>498.2</v>
+        <v>137.79</v>
       </c>
       <c r="J20" t="n">
-        <v>482.22</v>
+        <v>100.9</v>
       </c>
       <c r="K20" t="n">
-        <v>3.3</v>
+        <v>36.6</v>
       </c>
       <c r="L20" t="n">
-        <v>62.09</v>
+        <v>69.56</v>
       </c>
       <c r="M20" t="n">
-        <v>0.79</v>
+        <v>3.01</v>
       </c>
       <c r="N20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0.093</v>
+        <v>0.204</v>
       </c>
       <c r="Q20" t="n">
-        <v>852</v>
+        <v>1475</v>
       </c>
       <c r="R20" t="n">
-        <v>8.380000000000001</v>
+        <v>51.5</v>
       </c>
       <c r="S20" t="n">
         <v>7</v>
       </c>
       <c r="T20" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>14.66</v>
+        <v>0.95</v>
       </c>
       <c r="W20" t="n">
-        <v>14.4</v>
+        <v>5.28</v>
       </c>
       <c r="X20" t="n">
-        <v>0.01</v>
+        <v>0.52</v>
       </c>
       <c r="Y20" t="b">
         <v>1</v>
       </c>
       <c r="Z20" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="AA20" t="n">
-        <v>489.28</v>
+        <v>122.45</v>
       </c>
       <c r="AB20" t="n">
-        <v>488.46</v>
+        <v>115.46</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.7</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -2466,78 +2466,78 @@
         <v>17</v>
       </c>
       <c r="F21" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="G21" t="n">
         <v>25</v>
       </c>
       <c r="H21" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>122</v>
+      </c>
+      <c r="J21" t="n">
+        <v>83.06</v>
+      </c>
+      <c r="K21" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="L21" t="n">
+        <v>72.53</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1</v>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>0.049</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>859</v>
+      </c>
+      <c r="R21" t="n">
+        <v>91.8</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="U21" t="n">
+        <v>82</v>
+      </c>
+      <c r="V21" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W21" t="n">
+        <v>9.710000000000001</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>137.79</v>
-      </c>
-      <c r="J21" t="n">
-        <v>100.9</v>
-      </c>
-      <c r="K21" t="n">
-        <v>36.6</v>
-      </c>
-      <c r="L21" t="n">
-        <v>69.56</v>
-      </c>
-      <c r="M21" t="n">
-        <v>3.01</v>
-      </c>
-      <c r="N21" t="n">
-        <v>2</v>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>11-06-2026</t>
-        </is>
-      </c>
-      <c r="P21" t="n">
-        <v>0.203</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>1481</v>
-      </c>
-      <c r="R21" t="n">
-        <v>51.6</v>
-      </c>
-      <c r="S21" t="n">
-        <v>7</v>
-      </c>
-      <c r="T21" t="n">
-        <v>22</v>
-      </c>
-      <c r="U21" t="n">
-        <v>0</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="W21" t="n">
-        <v>5.28</v>
-      </c>
-      <c r="X21" t="n">
-        <v>0.52</v>
       </c>
       <c r="Y21" t="b">
         <v>1</v>
       </c>
       <c r="Z21" t="n">
-        <v>5</v>
+        <v>3.67</v>
       </c>
       <c r="AA21" t="n">
-        <v>122.45</v>
+        <v>107.79</v>
       </c>
       <c r="AB21" t="n">
-        <v>115.46</v>
+        <v>69.98</v>
       </c>
       <c r="AC21" t="n">
-        <v>-5.5</v>
+        <v>137.6</v>
       </c>
     </row>
     <row r="22">
@@ -2595,13 +2595,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.276</v>
+        <v>1.252</v>
       </c>
       <c r="Q22" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="R22" t="n">
-        <v>75.59999999999999</v>
+        <v>76.8</v>
       </c>
       <c r="S22" t="n">
         <v>-1</v>
@@ -2619,7 +2619,7 @@
         <v>-0.18</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y22" t="b">
         <v>0</v>
@@ -2695,10 +2695,10 @@
         <v>0.001</v>
       </c>
       <c r="Q23" t="n">
-        <v>361431</v>
+        <v>358502</v>
       </c>
       <c r="R23" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="S23" t="n">
         <v>7</v>
@@ -2789,13 +2789,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0.053</v>
+        <v>0.054</v>
       </c>
       <c r="Q24" t="n">
-        <v>4988</v>
+        <v>4888</v>
       </c>
       <c r="R24" t="n">
-        <v>32.5</v>
+        <v>31.8</v>
       </c>
       <c r="S24" t="n">
         <v>-25</v>
@@ -2834,12 +2834,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>THOMAS COOK (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -2851,92 +2851,92 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F25" t="n">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H25" t="n">
         <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>508.3</v>
+        <v>106.09</v>
       </c>
       <c r="J25" t="n">
-        <v>545.03</v>
+        <v>109.31</v>
       </c>
       <c r="K25" t="n">
-        <v>-6.7</v>
+        <v>-2.9</v>
       </c>
       <c r="L25" t="n">
-        <v>69.90000000000001</v>
+        <v>72.34</v>
       </c>
       <c r="M25" t="n">
-        <v>1.09</v>
+        <v>48.4</v>
       </c>
       <c r="N25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0.034</v>
+        <v>0.971</v>
       </c>
       <c r="Q25" t="n">
-        <v>3215</v>
+        <v>4986</v>
       </c>
       <c r="R25" t="n">
-        <v>21.8</v>
+        <v>40</v>
       </c>
       <c r="S25" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>97</v>
+        <v>42</v>
       </c>
       <c r="U25" t="n">
-        <v>53</v>
+        <v>8</v>
       </c>
       <c r="V25" t="n">
-        <v>3.73</v>
+        <v>1.25</v>
       </c>
       <c r="W25" t="n">
-        <v>19.8</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="X25" t="n">
-        <v>0.62</v>
+        <v>0.06</v>
       </c>
       <c r="Y25" t="b">
         <v>1</v>
       </c>
       <c r="Z25" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="AA25" t="n">
-        <v>527.91</v>
+        <v>105.17</v>
       </c>
       <c r="AB25" t="n">
-        <v>561.66</v>
+        <v>113.53</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.8</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>THOMAS COOK (INDIA) LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -2948,81 +2948,81 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F26" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H26" t="n">
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>106.09</v>
+        <v>508.3</v>
       </c>
       <c r="J26" t="n">
-        <v>109.31</v>
+        <v>545.03</v>
       </c>
       <c r="K26" t="n">
-        <v>-2.9</v>
+        <v>-6.7</v>
       </c>
       <c r="L26" t="n">
-        <v>72.34</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>48.4</v>
+        <v>1.09</v>
       </c>
       <c r="N26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0.969</v>
+        <v>0.033</v>
       </c>
       <c r="Q26" t="n">
-        <v>4995</v>
+        <v>3255</v>
       </c>
       <c r="R26" t="n">
-        <v>40.1</v>
+        <v>22</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="T26" t="n">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="U26" t="n">
-        <v>8</v>
+        <v>53</v>
       </c>
       <c r="V26" t="n">
-        <v>1.25</v>
+        <v>3.73</v>
       </c>
       <c r="W26" t="n">
-        <v>9.710000000000001</v>
+        <v>19.8</v>
       </c>
       <c r="X26" t="n">
-        <v>0.06</v>
+        <v>0.62</v>
       </c>
       <c r="Y26" t="b">
         <v>1</v>
       </c>
       <c r="Z26" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="AA26" t="n">
-        <v>105.17</v>
+        <v>527.91</v>
       </c>
       <c r="AB26" t="n">
-        <v>113.53</v>
+        <v>561.66</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.1</v>
+        <v>0.8</v>
       </c>
     </row>
     <row r="27">
@@ -3080,13 +3080,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0.268</v>
+        <v>0.264</v>
       </c>
       <c r="Q27" t="n">
-        <v>1107</v>
+        <v>1124</v>
       </c>
       <c r="R27" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="S27" t="n">
         <v>12</v>
@@ -3180,10 +3180,10 @@
         <v>0.149</v>
       </c>
       <c r="Q28" t="n">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="R28" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="S28" t="n">
         <v>12</v>
@@ -3222,12 +3222,12 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -3239,90 +3239,92 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="G29" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>750.4</v>
+        <v>173.81</v>
       </c>
       <c r="J29" t="n">
-        <v>815.16</v>
+        <v>175.74</v>
       </c>
       <c r="K29" t="n">
-        <v>-7.9</v>
+        <v>-1.1</v>
       </c>
       <c r="L29" t="n">
-        <v>73.2</v>
+        <v>74.59</v>
       </c>
       <c r="M29" t="n">
-        <v>1.24</v>
+        <v>0.49</v>
       </c>
       <c r="N29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0.163</v>
+        <v>0.023</v>
       </c>
       <c r="Q29" t="n">
-        <v>760</v>
+        <v>2099</v>
       </c>
       <c r="R29" t="n">
-        <v>13.8</v>
+        <v>48.2</v>
       </c>
       <c r="S29" t="n">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="T29" t="n">
-        <v>11.55</v>
+        <v>17</v>
       </c>
       <c r="U29" t="n">
-        <v>204</v>
+        <v>83</v>
       </c>
       <c r="V29" t="n">
-        <v>6.84</v>
+        <v>0.8</v>
       </c>
       <c r="W29" t="n">
-        <v>50.7</v>
+        <v>30.3</v>
       </c>
       <c r="X29" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="Y29" t="b">
         <v>1</v>
       </c>
       <c r="Z29" t="n">
-        <v>16.07</v>
+        <v>23</v>
       </c>
       <c r="AA29" t="n">
-        <v>744.08</v>
-      </c>
-      <c r="AB29" t="inlineStr"/>
+        <v>191.3</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>547.3200000000001</v>
+      </c>
       <c r="AC29" t="n">
-        <v>-17.5</v>
+        <v>-88</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -3334,81 +3336,79 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F30" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H30" t="n">
         <v>0</v>
       </c>
       <c r="I30" t="n">
-        <v>173.81</v>
+        <v>750.4</v>
       </c>
       <c r="J30" t="n">
-        <v>175.74</v>
+        <v>815.16</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.1</v>
+        <v>-7.9</v>
       </c>
       <c r="L30" t="n">
-        <v>74.59</v>
+        <v>73.2</v>
       </c>
       <c r="M30" t="n">
-        <v>0.49</v>
+        <v>1.24</v>
       </c>
       <c r="N30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0.022</v>
+        <v>0.16</v>
       </c>
       <c r="Q30" t="n">
-        <v>2197</v>
+        <v>776</v>
       </c>
       <c r="R30" t="n">
-        <v>50.4</v>
+        <v>14.1</v>
       </c>
       <c r="S30" t="n">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="T30" t="n">
-        <v>17</v>
+        <v>11.55</v>
       </c>
       <c r="U30" t="n">
-        <v>83</v>
+        <v>204</v>
       </c>
       <c r="V30" t="n">
-        <v>0.8</v>
+        <v>6.84</v>
       </c>
       <c r="W30" t="n">
-        <v>30.3</v>
+        <v>50.7</v>
       </c>
       <c r="X30" t="n">
-        <v>0.2</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="Y30" t="b">
         <v>1</v>
       </c>
       <c r="Z30" t="n">
-        <v>23</v>
+        <v>16.07</v>
       </c>
       <c r="AA30" t="n">
-        <v>191.3</v>
-      </c>
-      <c r="AB30" t="n">
-        <v>547.3200000000001</v>
-      </c>
+        <v>744.08</v>
+      </c>
+      <c r="AB30" t="inlineStr"/>
       <c r="AC30" t="n">
-        <v>-88</v>
+        <v>-17.5</v>
       </c>
     </row>
     <row r="31">
@@ -3466,13 +3466,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0.399</v>
+        <v>0.398</v>
       </c>
       <c r="Q31" t="n">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="R31" t="n">
-        <v>1196</v>
+        <v>1199</v>
       </c>
       <c r="S31" t="n">
         <v>-61</v>
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.194</v>
+        <v>1.182</v>
       </c>
       <c r="Q32" t="n">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="R32" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="S32" t="n">
         <v>-1</v>
@@ -3604,16 +3604,16 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EUROPRATIK</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Euro Pratik Sales Limited</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3621,92 +3621,90 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="G33" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="H33" t="n">
         <v>0</v>
       </c>
       <c r="I33" t="n">
-        <v>260.05</v>
+        <v>171.86</v>
       </c>
       <c r="J33" t="n">
-        <v>257.65</v>
+        <v>182.69</v>
       </c>
       <c r="K33" t="n">
-        <v>0.9</v>
+        <v>-5.9</v>
       </c>
       <c r="L33" t="n">
-        <v>70.09</v>
+        <v>69.05</v>
       </c>
       <c r="M33" t="n">
-        <v>1.64</v>
+        <v>0.74</v>
       </c>
       <c r="N33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0.062</v>
+        <v>0.126</v>
       </c>
       <c r="Q33" t="n">
-        <v>2658</v>
+        <v>589</v>
       </c>
       <c r="R33" t="n">
-        <v>46.3</v>
+        <v>14</v>
       </c>
       <c r="S33" t="n">
-        <v>-3</v>
+        <v>61</v>
       </c>
       <c r="T33" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="U33" t="n">
-        <v>3</v>
+        <v>82</v>
       </c>
       <c r="V33" t="n">
-        <v>1.05</v>
+        <v>3.07</v>
       </c>
       <c r="W33" t="n">
-        <v>29.6</v>
+        <v>42.7</v>
       </c>
       <c r="X33" t="n">
-        <v>0.03</v>
+        <v>0.35</v>
       </c>
       <c r="Y33" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="AA33" t="n">
-        <v>293.27</v>
-      </c>
-      <c r="AB33" t="n">
-        <v>276.82</v>
-      </c>
+        <v>171.19</v>
+      </c>
+      <c r="AB33" t="inlineStr"/>
       <c r="AC33" t="n">
-        <v>1</v>
+        <v>-11.1</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -3718,94 +3716,96 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F34" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G34" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I34" t="n">
-        <v>171.86</v>
+        <v>113.76</v>
       </c>
       <c r="J34" t="n">
-        <v>182.69</v>
+        <v>113.42</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.9</v>
+        <v>0.3</v>
       </c>
       <c r="L34" t="n">
-        <v>69.05</v>
+        <v>73.48</v>
       </c>
       <c r="M34" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="N34" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0.125</v>
+        <v>0.298</v>
       </c>
       <c r="Q34" t="n">
-        <v>590</v>
+        <v>218</v>
       </c>
       <c r="R34" t="n">
-        <v>14</v>
+        <v>25.9</v>
       </c>
       <c r="S34" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
       <c r="T34" t="n">
-        <v>15</v>
+        <v>12.07</v>
       </c>
       <c r="U34" t="n">
-        <v>82</v>
+        <v>-29</v>
       </c>
       <c r="V34" t="n">
-        <v>3.07</v>
+        <v>1.02</v>
       </c>
       <c r="W34" t="n">
-        <v>42.7</v>
+        <v>7.92</v>
       </c>
       <c r="X34" t="n">
-        <v>0.35</v>
+        <v>0.98</v>
       </c>
       <c r="Y34" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z34" t="n">
-        <v>12</v>
+        <v>4.11</v>
       </c>
       <c r="AA34" t="n">
-        <v>171.19</v>
-      </c>
-      <c r="AB34" t="inlineStr"/>
+        <v>111.24</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>119.79</v>
+      </c>
       <c r="AC34" t="n">
-        <v>-11.1</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>AJMERA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3816,89 +3816,89 @@
         <v>25</v>
       </c>
       <c r="F35" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G35" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H35" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>113.76</v>
+        <v>115.69</v>
       </c>
       <c r="J35" t="n">
-        <v>113.42</v>
+        <v>114.86</v>
       </c>
       <c r="K35" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="L35" t="n">
-        <v>73.48</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>0.65</v>
+        <v>7.36</v>
       </c>
       <c r="N35" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0.3</v>
+        <v>0.317</v>
       </c>
       <c r="Q35" t="n">
-        <v>217</v>
+        <v>2324</v>
       </c>
       <c r="R35" t="n">
-        <v>25.8</v>
+        <v>20</v>
       </c>
       <c r="S35" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="T35" t="n">
-        <v>12.07</v>
+        <v>46</v>
       </c>
       <c r="U35" t="n">
-        <v>-29</v>
+        <v>-4</v>
       </c>
       <c r="V35" t="n">
-        <v>1.02</v>
+        <v>1.17</v>
       </c>
       <c r="W35" t="n">
-        <v>7.92</v>
+        <v>14.2</v>
       </c>
       <c r="X35" t="n">
-        <v>0.98</v>
+        <v>0.46</v>
       </c>
       <c r="Y35" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>4.11</v>
+        <v>38</v>
       </c>
       <c r="AA35" t="n">
-        <v>111.24</v>
+        <v>125.01</v>
       </c>
       <c r="AB35" t="n">
-        <v>119.79</v>
+        <v>314.5</v>
       </c>
       <c r="AC35" t="n">
-        <v>-2</v>
+        <v>-12.4</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AJMERA</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -3913,93 +3913,93 @@
         <v>25</v>
       </c>
       <c r="F36" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="G36" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H36" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I36" t="n">
+        <v>41.37</v>
+      </c>
+      <c r="J36" t="n">
+        <v>42.65</v>
+      </c>
+      <c r="K36" t="n">
+        <v>-3</v>
+      </c>
+      <c r="L36" t="n">
+        <v>71.79000000000001</v>
+      </c>
+      <c r="M36" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="N36" t="n">
+        <v>24</v>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>01-09-2026</t>
+        </is>
+      </c>
+      <c r="P36" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>413</v>
+      </c>
+      <c r="R36" t="n">
+        <v>102</v>
+      </c>
+      <c r="S36" t="n">
+        <v>246</v>
+      </c>
+      <c r="T36" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="U36" t="n">
+        <v>10</v>
+      </c>
+      <c r="V36" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W36" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="X36" t="n">
         <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>115.69</v>
-      </c>
-      <c r="J36" t="n">
-        <v>114.86</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="L36" t="n">
-        <v>69.73999999999999</v>
-      </c>
-      <c r="M36" t="n">
-        <v>7.36</v>
-      </c>
-      <c r="N36" t="n">
-        <v>4</v>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>04-06-2026</t>
-        </is>
-      </c>
-      <c r="P36" t="n">
-        <v>0.323</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>2279</v>
-      </c>
-      <c r="R36" t="n">
-        <v>19.6</v>
-      </c>
-      <c r="S36" t="n">
-        <v>18</v>
-      </c>
-      <c r="T36" t="n">
-        <v>46</v>
-      </c>
-      <c r="U36" t="n">
-        <v>-4</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="W36" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="X36" t="n">
-        <v>0.46</v>
       </c>
       <c r="Y36" t="b">
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>38</v>
+        <v>4.21</v>
       </c>
       <c r="AA36" t="n">
-        <v>125.01</v>
+        <v>40.69</v>
       </c>
       <c r="AB36" t="n">
-        <v>314.5</v>
+        <v>39.67</v>
       </c>
       <c r="AC36" t="n">
-        <v>-12.4</v>
+        <v>-0.1</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4010,186 +4010,184 @@
         <v>25</v>
       </c>
       <c r="F37" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H37" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
-        <v>41.37</v>
+        <v>428.85</v>
       </c>
       <c r="J37" t="n">
-        <v>42.65</v>
+        <v>474.82</v>
       </c>
       <c r="K37" t="n">
-        <v>-3</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>71.79000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="M37" t="n">
-        <v>1.45</v>
+        <v>10.22</v>
       </c>
       <c r="N37" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0.353</v>
+        <v>0.277</v>
       </c>
       <c r="Q37" t="n">
-        <v>411</v>
+        <v>3686</v>
       </c>
       <c r="R37" t="n">
-        <v>102</v>
+        <v>25.8</v>
       </c>
       <c r="S37" t="n">
-        <v>246</v>
+        <v>2</v>
       </c>
       <c r="T37" t="n">
-        <v>0.91</v>
+        <v>127</v>
       </c>
       <c r="U37" t="n">
-        <v>10</v>
+        <v>-14</v>
       </c>
       <c r="V37" t="n">
-        <v>0.14</v>
+        <v>6.41</v>
       </c>
       <c r="W37" t="n">
-        <v>2.16</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="X37" t="n">
-        <v>-0</v>
+        <v>1.05</v>
       </c>
       <c r="Y37" t="b">
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>4.21</v>
+        <v>21</v>
       </c>
       <c r="AA37" t="n">
-        <v>40.69</v>
+        <v>447.6</v>
       </c>
       <c r="AB37" t="n">
-        <v>39.67</v>
+        <v>433.97</v>
       </c>
       <c r="AC37" t="n">
-        <v>-0.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Watchlist</t>
+          <t>Fundamental Watch</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F38" t="n">
+        <v>14</v>
+      </c>
+      <c r="G38" t="n">
         <v>5</v>
-      </c>
-      <c r="G38" t="n">
-        <v>10</v>
       </c>
       <c r="H38" t="n">
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>428.85</v>
+        <v>728.65</v>
       </c>
       <c r="J38" t="n">
-        <v>474.82</v>
+        <v>717.77</v>
       </c>
       <c r="K38" t="n">
-        <v>-9.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="L38" t="n">
-        <v>70.55</v>
+        <v>61.71</v>
       </c>
       <c r="M38" t="n">
-        <v>10.22</v>
+        <v>1.61</v>
       </c>
       <c r="N38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0.278</v>
+        <v>0.706</v>
       </c>
       <c r="Q38" t="n">
-        <v>3673</v>
-      </c>
-      <c r="R38" t="n">
-        <v>25.7</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="R38" t="inlineStr"/>
       <c r="S38" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="T38" t="n">
-        <v>127</v>
+        <v>11.91</v>
       </c>
       <c r="U38" t="n">
-        <v>-14</v>
+        <v>-184</v>
       </c>
       <c r="V38" t="n">
-        <v>6.41</v>
+        <v>31.98</v>
       </c>
       <c r="W38" t="n">
-        <v>9.890000000000001</v>
+        <v>0.27</v>
       </c>
       <c r="X38" t="n">
-        <v>1.05</v>
+        <v>0.1</v>
       </c>
       <c r="Y38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z38" t="n">
-        <v>21</v>
+        <v>57.93</v>
       </c>
       <c r="AA38" t="n">
-        <v>447.6</v>
+        <v>729.73</v>
       </c>
       <c r="AB38" t="n">
-        <v>433.97</v>
+        <v>761.0700000000001</v>
       </c>
       <c r="AC38" t="n">
-        <v>6.3</v>
+        <v>-8.300000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -4201,94 +4199,94 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="F39" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="G39" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H39" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I39" t="n">
-        <v>728.65</v>
+        <v>54.77</v>
       </c>
       <c r="J39" t="n">
-        <v>717.77</v>
+        <v>53.51</v>
       </c>
       <c r="K39" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="L39" t="n">
-        <v>61.71</v>
+        <v>67.23</v>
       </c>
       <c r="M39" t="n">
-        <v>1.61</v>
+        <v>2.03</v>
       </c>
       <c r="N39" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0.712</v>
+        <v>1.75</v>
       </c>
       <c r="Q39" t="n">
-        <v>226</v>
+        <v>116</v>
       </c>
       <c r="R39" t="inlineStr"/>
       <c r="S39" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="T39" t="n">
-        <v>11.91</v>
+        <v>2.47</v>
       </c>
       <c r="U39" t="n">
-        <v>-184</v>
+        <v>-3779</v>
       </c>
       <c r="V39" t="n">
-        <v>31.98</v>
+        <v>-0.05</v>
       </c>
       <c r="W39" t="n">
-        <v>0.27</v>
+        <v>-1.26</v>
       </c>
       <c r="X39" t="n">
-        <v>0.1</v>
+        <v>0.8</v>
       </c>
       <c r="Y39" t="b">
         <v>1</v>
       </c>
       <c r="Z39" t="n">
-        <v>57.93</v>
+        <v>3</v>
       </c>
       <c r="AA39" t="n">
-        <v>729.73</v>
+        <v>54.13</v>
       </c>
       <c r="AB39" t="n">
-        <v>761.0700000000001</v>
+        <v>55.11</v>
       </c>
       <c r="AC39" t="n">
-        <v>-8.300000000000001</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4296,90 +4294,92 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="G40" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I40" t="n">
-        <v>54.77</v>
+        <v>262.35</v>
       </c>
       <c r="J40" t="n">
-        <v>53.51</v>
+        <v>269.7</v>
       </c>
       <c r="K40" t="n">
-        <v>2.4</v>
+        <v>-2.7</v>
       </c>
       <c r="L40" t="n">
-        <v>67.23</v>
+        <v>73.09</v>
       </c>
       <c r="M40" t="n">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="N40" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.765</v>
+        <v>0.1</v>
       </c>
       <c r="Q40" t="n">
-        <v>115</v>
-      </c>
-      <c r="R40" t="inlineStr"/>
+        <v>1481</v>
+      </c>
+      <c r="R40" t="n">
+        <v>13.4</v>
+      </c>
       <c r="S40" t="n">
         <v>6</v>
       </c>
       <c r="T40" t="n">
-        <v>2.47</v>
+        <v>46</v>
       </c>
       <c r="U40" t="n">
-        <v>-3779</v>
+        <v>18</v>
       </c>
       <c r="V40" t="n">
-        <v>-0.05</v>
+        <v>4.31</v>
       </c>
       <c r="W40" t="n">
-        <v>-1.26</v>
+        <v>13.6</v>
       </c>
       <c r="X40" t="n">
-        <v>0.8</v>
+        <v>0.28</v>
       </c>
       <c r="Y40" t="b">
         <v>1</v>
       </c>
       <c r="Z40" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="AA40" t="n">
-        <v>54.13</v>
+        <v>268.11</v>
       </c>
       <c r="AB40" t="n">
-        <v>55.11</v>
+        <v>293.23</v>
       </c>
       <c r="AC40" t="n">
-        <v>-0.4</v>
+        <v>-9.199999999999999</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -4394,93 +4394,93 @@
         <v>17</v>
       </c>
       <c r="F41" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I41" t="n">
-        <v>262.35</v>
+        <v>55.23</v>
       </c>
       <c r="J41" t="n">
-        <v>269.7</v>
+        <v>60.15</v>
       </c>
       <c r="K41" t="n">
-        <v>-2.7</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>73.09</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0.099</v>
+        <v>0.188</v>
       </c>
       <c r="Q41" t="n">
-        <v>1488</v>
+        <v>478</v>
       </c>
       <c r="R41" t="n">
-        <v>13.5</v>
+        <v>11.9</v>
       </c>
       <c r="S41" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="T41" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="U41" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="V41" t="n">
-        <v>4.31</v>
+        <v>1.22</v>
       </c>
       <c r="W41" t="n">
-        <v>13.6</v>
+        <v>12</v>
       </c>
       <c r="X41" t="n">
-        <v>0.28</v>
+        <v>0.58</v>
       </c>
       <c r="Y41" t="b">
         <v>1</v>
       </c>
       <c r="Z41" t="n">
-        <v>12</v>
+        <v>3.4</v>
       </c>
       <c r="AA41" t="n">
-        <v>268.11</v>
+        <v>57.72</v>
       </c>
       <c r="AB41" t="n">
-        <v>293.23</v>
+        <v>59.16</v>
       </c>
       <c r="AC41" t="n">
-        <v>-9.199999999999999</v>
+        <v>-10.5</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>GRM OVERSEAS LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4488,96 +4488,96 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="F42" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>-2</v>
+        <v>0</v>
       </c>
       <c r="I42" t="n">
-        <v>55.23</v>
+        <v>86.03</v>
       </c>
       <c r="J42" t="n">
-        <v>60.15</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>-8.199999999999999</v>
+        <v>-10</v>
       </c>
       <c r="L42" t="n">
-        <v>73.01000000000001</v>
+        <v>71.72</v>
       </c>
       <c r="M42" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="N42" t="n">
+        <v>6</v>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>24-06-2026</t>
+        </is>
+      </c>
+      <c r="P42" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>1792</v>
+      </c>
+      <c r="R42" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="S42" t="n">
+        <v>39</v>
+      </c>
+      <c r="T42" t="n">
+        <v>31</v>
+      </c>
+      <c r="U42" t="n">
+        <v>8</v>
+      </c>
+      <c r="V42" t="n">
         <v>0.9</v>
       </c>
-      <c r="N42" t="n">
-        <v>2</v>
-      </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>06-08-2026</t>
-        </is>
-      </c>
-      <c r="P42" t="n">
-        <v>0.189</v>
-      </c>
-      <c r="Q42" t="n">
-        <v>477</v>
-      </c>
-      <c r="R42" t="n">
-        <v>11.9</v>
-      </c>
-      <c r="S42" t="n">
-        <v>19</v>
-      </c>
-      <c r="T42" t="n">
-        <v>21</v>
-      </c>
-      <c r="U42" t="n">
-        <v>20</v>
-      </c>
-      <c r="V42" t="n">
-        <v>1.22</v>
-      </c>
       <c r="W42" t="n">
-        <v>12</v>
+        <v>11.3</v>
       </c>
       <c r="X42" t="n">
-        <v>0.58</v>
+        <v>0.67</v>
       </c>
       <c r="Y42" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z42" t="n">
-        <v>3.4</v>
+        <v>9</v>
       </c>
       <c r="AA42" t="n">
-        <v>57.72</v>
+        <v>91.13</v>
       </c>
       <c r="AB42" t="n">
-        <v>59.16</v>
+        <v>186.31</v>
       </c>
       <c r="AC42" t="n">
-        <v>-10.5</v>
+        <v>-46.6</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4585,10 +4585,10 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="F43" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -4597,84 +4597,84 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>86.03</v>
+        <v>171.87</v>
       </c>
       <c r="J43" t="n">
-        <v>95.54000000000001</v>
+        <v>173.91</v>
       </c>
       <c r="K43" t="n">
-        <v>-10</v>
+        <v>-1.2</v>
       </c>
       <c r="L43" t="n">
-        <v>71.72</v>
+        <v>65.64</v>
       </c>
       <c r="M43" t="n">
-        <v>10.87</v>
+        <v>2.61</v>
       </c>
       <c r="N43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0.61</v>
+        <v>0.137</v>
       </c>
       <c r="Q43" t="n">
-        <v>1781</v>
+        <v>1907</v>
       </c>
       <c r="R43" t="n">
-        <v>32.1</v>
+        <v>20.2</v>
       </c>
       <c r="S43" t="n">
-        <v>39</v>
+        <v>-3</v>
       </c>
       <c r="T43" t="n">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="U43" t="n">
-        <v>8</v>
+        <v>-4</v>
       </c>
       <c r="V43" t="n">
-        <v>0.9</v>
+        <v>2.36</v>
       </c>
       <c r="W43" t="n">
-        <v>11.3</v>
+        <v>14.2</v>
       </c>
       <c r="X43" t="n">
-        <v>0.67</v>
+        <v>0.01</v>
       </c>
       <c r="Y43" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z43" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="AA43" t="n">
-        <v>91.13</v>
+        <v>183.37</v>
       </c>
       <c r="AB43" t="n">
-        <v>186.31</v>
+        <v>190.08</v>
       </c>
       <c r="AC43" t="n">
-        <v>-46.6</v>
+        <v>-15.7</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4685,7 +4685,7 @@
         <v>20</v>
       </c>
       <c r="F44" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -4694,84 +4694,84 @@
         <v>0</v>
       </c>
       <c r="I44" t="n">
-        <v>171.87</v>
+        <v>266.1</v>
       </c>
       <c r="J44" t="n">
-        <v>173.91</v>
+        <v>292.28</v>
       </c>
       <c r="K44" t="n">
-        <v>-1.2</v>
+        <v>-9</v>
       </c>
       <c r="L44" t="n">
-        <v>65.64</v>
+        <v>70.45</v>
       </c>
       <c r="M44" t="n">
-        <v>2.61</v>
+        <v>1.29</v>
       </c>
       <c r="N44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0.137</v>
+        <v>0.083</v>
       </c>
       <c r="Q44" t="n">
-        <v>1908</v>
+        <v>1546</v>
       </c>
       <c r="R44" t="n">
-        <v>20.2</v>
+        <v>19.6</v>
       </c>
       <c r="S44" t="n">
-        <v>-3</v>
+        <v>13</v>
       </c>
       <c r="T44" t="n">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="U44" t="n">
         <v>-4</v>
       </c>
       <c r="V44" t="n">
-        <v>2.36</v>
+        <v>2.56</v>
       </c>
       <c r="W44" t="n">
-        <v>14.2</v>
+        <v>19.9</v>
       </c>
       <c r="X44" t="n">
-        <v>0.01</v>
+        <v>0.13</v>
       </c>
       <c r="Y44" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z44" t="n">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AA44" t="n">
-        <v>183.37</v>
+        <v>296.21</v>
       </c>
       <c r="AB44" t="n">
-        <v>190.08</v>
+        <v>321.82</v>
       </c>
       <c r="AC44" t="n">
-        <v>-15.7</v>
+        <v>-10.8</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MBEL</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>M &amp; B Engineering Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4788,184 +4788,174 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="I45" t="n">
-        <v>266.1</v>
+        <v>28.25</v>
       </c>
       <c r="J45" t="n">
-        <v>292.28</v>
+        <v>34.54</v>
       </c>
       <c r="K45" t="n">
-        <v>-9</v>
+        <v>-18.2</v>
       </c>
       <c r="L45" t="n">
-        <v>70.45</v>
+        <v>61.81</v>
       </c>
       <c r="M45" t="n">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="N45" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.278</v>
       </c>
       <c r="Q45" t="n">
-        <v>1524</v>
+        <v>317</v>
       </c>
       <c r="R45" t="n">
-        <v>19.3</v>
+        <v>16.7</v>
       </c>
       <c r="S45" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="T45" t="n">
-        <v>21</v>
+        <v>2.79</v>
       </c>
       <c r="U45" t="n">
-        <v>-4</v>
+        <v>-30</v>
       </c>
       <c r="V45" t="n">
-        <v>2.56</v>
+        <v>0.21</v>
       </c>
       <c r="W45" t="n">
-        <v>19.9</v>
+        <v>17.6</v>
       </c>
       <c r="X45" t="n">
-        <v>0.13</v>
+        <v>0.31</v>
       </c>
       <c r="Y45" t="b">
         <v>0</v>
       </c>
       <c r="Z45" t="n">
-        <v>8</v>
+        <v>1.83</v>
       </c>
       <c r="AA45" t="n">
-        <v>296.21</v>
+        <v>30.71</v>
       </c>
       <c r="AB45" t="n">
-        <v>321.82</v>
+        <v>33.12</v>
       </c>
       <c r="AC45" t="n">
-        <v>-10.8</v>
+        <v>-12.2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Fundamental Watch</t>
+          <t>Avoid</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="F46" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G46" t="n">
+        <v>5</v>
+      </c>
+      <c r="H46" t="n">
         <v>0</v>
       </c>
-      <c r="H46" t="n">
-        <v>-2</v>
-      </c>
       <c r="I46" t="n">
-        <v>28.25</v>
+        <v>66.14</v>
       </c>
       <c r="J46" t="n">
-        <v>34.54</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-18.2</v>
+        <v>3.3</v>
       </c>
       <c r="L46" t="n">
-        <v>61.81</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="N46" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0.295</v>
+        <v>0.037</v>
       </c>
       <c r="Q46" t="n">
-        <v>298</v>
+        <v>829</v>
       </c>
       <c r="R46" t="n">
-        <v>15.7</v>
-      </c>
-      <c r="S46" t="n">
-        <v>16</v>
-      </c>
+        <v>19.9</v>
+      </c>
+      <c r="S46" t="inlineStr"/>
       <c r="T46" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="U46" t="n">
-        <v>-30</v>
-      </c>
+        <v>12.31</v>
+      </c>
+      <c r="U46" t="inlineStr"/>
       <c r="V46" t="n">
-        <v>0.21</v>
-      </c>
-      <c r="W46" t="n">
-        <v>17.6</v>
-      </c>
+        <v>0.8</v>
+      </c>
+      <c r="W46" t="inlineStr"/>
       <c r="X46" t="n">
-        <v>0.31</v>
+        <v>0.11</v>
       </c>
       <c r="Y46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z46" t="n">
-        <v>1.83</v>
+        <v>12.14</v>
       </c>
       <c r="AA46" t="n">
-        <v>30.71</v>
-      </c>
-      <c r="AB46" t="n">
-        <v>33.12</v>
-      </c>
-      <c r="AC46" t="n">
-        <v>-12.2</v>
-      </c>
+        <v>67.05</v>
+      </c>
+      <c r="AB46" t="inlineStr"/>
+      <c r="AC46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4973,167 +4963,80 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F47" t="n">
+        <v>8</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-2</v>
+      </c>
+      <c r="I47" t="n">
+        <v>84.28</v>
+      </c>
+      <c r="J47" t="n">
+        <v>100.33</v>
+      </c>
+      <c r="K47" t="n">
+        <v>-16</v>
+      </c>
+      <c r="L47" t="n">
+        <v>71.89</v>
+      </c>
+      <c r="M47" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="N47" t="n">
+        <v>5</v>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>30-06-2026</t>
+        </is>
+      </c>
+      <c r="P47" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="Q47" t="n">
+        <v>866</v>
+      </c>
+      <c r="R47" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="S47" t="n">
         <v>9</v>
       </c>
-      <c r="G47" t="n">
-        <v>5</v>
-      </c>
-      <c r="H47" t="n">
+      <c r="T47" t="n">
+        <v>18.68</v>
+      </c>
+      <c r="U47" t="n">
+        <v>-36</v>
+      </c>
+      <c r="V47" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="W47" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="X47" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="Y47" t="b">
         <v>0</v>
       </c>
-      <c r="I47" t="n">
-        <v>66.14</v>
-      </c>
-      <c r="J47" t="n">
-        <v>64.04000000000001</v>
-      </c>
-      <c r="K47" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L47" t="n">
-        <v>64.29000000000001</v>
-      </c>
-      <c r="M47" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="N47" t="n">
-        <v>3</v>
-      </c>
-      <c r="O47" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-      <c r="P47" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="Q47" t="n">
-        <v>811</v>
-      </c>
-      <c r="R47" t="n">
-        <v>19.4</v>
-      </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="n">
-        <v>12.31</v>
-      </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="n">
-        <v>0.8</v>
-      </c>
-      <c r="W47" t="inlineStr"/>
-      <c r="X47" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="Y47" t="b">
-        <v>1</v>
-      </c>
       <c r="Z47" t="n">
-        <v>12.14</v>
+        <v>4.02</v>
       </c>
       <c r="AA47" t="n">
-        <v>67.05</v>
-      </c>
-      <c r="AB47" t="inlineStr"/>
-      <c r="AC47" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>WCIL</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>26</v>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Avoid</t>
-        </is>
-      </c>
-      <c r="E48" t="n">
-        <v>20</v>
-      </c>
-      <c r="F48" t="n">
-        <v>8</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-2</v>
-      </c>
-      <c r="I48" t="n">
-        <v>84.28</v>
-      </c>
-      <c r="J48" t="n">
-        <v>100.33</v>
-      </c>
-      <c r="K48" t="n">
-        <v>-16</v>
-      </c>
-      <c r="L48" t="n">
-        <v>71.89</v>
-      </c>
-      <c r="M48" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="N48" t="n">
-        <v>5</v>
-      </c>
-      <c r="O48" t="inlineStr">
-        <is>
-          <t>30-06-2026</t>
-        </is>
-      </c>
-      <c r="P48" t="n">
-        <v>0.073</v>
-      </c>
-      <c r="Q48" t="n">
-        <v>858</v>
-      </c>
-      <c r="R48" t="n">
-        <v>23.4</v>
-      </c>
-      <c r="S48" t="n">
-        <v>9</v>
-      </c>
-      <c r="T48" t="n">
-        <v>18.68</v>
-      </c>
-      <c r="U48" t="n">
-        <v>-36</v>
-      </c>
-      <c r="V48" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="W48" t="n">
-        <v>6.79</v>
-      </c>
-      <c r="X48" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="Y48" t="b">
-        <v>0</v>
-      </c>
-      <c r="Z48" t="n">
-        <v>4.02</v>
-      </c>
-      <c r="AA48" t="n">
         <v>91.31999999999999</v>
       </c>
-      <c r="AB48" t="n">
+      <c r="AB47" t="n">
         <v>103.73</v>
       </c>
-      <c r="AC48" t="n">
+      <c r="AC47" t="n">
         <v>-27.8</v>
       </c>
     </row>
@@ -5148,7 +5051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I48"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5259,19 +5162,19 @@
         <v>89.79000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>55.78</v>
+        <v>56.48</v>
       </c>
       <c r="E3" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
         <v>67.45999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>6.19</v>
+        <v>3.94</v>
       </c>
       <c r="H3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -5282,70 +5185,70 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>APLLTD</t>
+          <t>BHAGERIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Alembic Pharmaceuticals Limited</t>
+          <t>Bhageria Industries Limited</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>826.9</v>
+        <v>276.35</v>
       </c>
       <c r="D4" t="n">
-        <v>746.02</v>
+        <v>217.8</v>
       </c>
       <c r="E4" t="n">
-        <v>10.8</v>
+        <v>26.9</v>
       </c>
       <c r="F4" t="n">
-        <v>69.61</v>
+        <v>71.75</v>
       </c>
       <c r="G4" t="n">
-        <v>7.69</v>
+        <v>0.82</v>
       </c>
       <c r="H4" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>18-06-2026</t>
+          <t>26-08-2026</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BHAGERIA</t>
+          <t>APLLTD</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Bhageria Industries Limited</t>
+          <t>Alembic Pharmaceuticals Limited</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>276.35</v>
+        <v>826.9</v>
       </c>
       <c r="D5" t="n">
-        <v>217.8</v>
+        <v>746.02</v>
       </c>
       <c r="E5" t="n">
-        <v>26.9</v>
+        <v>10.8</v>
       </c>
       <c r="F5" t="n">
-        <v>71.75</v>
+        <v>69.61</v>
       </c>
       <c r="G5" t="n">
-        <v>0.82</v>
+        <v>7.69</v>
       </c>
       <c r="H5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>26-08-2026</t>
+          <t>18-06-2026</t>
         </is>
       </c>
     </row>
@@ -5492,105 +5395,105 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ALEMBICLTD</t>
+          <t>ASAHISONG</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alembic Limited</t>
+          <t>ASAHI SONGWON COLORS LIMITED</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>100.14</v>
+        <v>367.9</v>
       </c>
       <c r="D10" t="n">
-        <v>91.62</v>
+        <v>338.1</v>
       </c>
       <c r="E10" t="n">
-        <v>9.300000000000001</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="F10" t="n">
-        <v>70.88</v>
+        <v>66.73</v>
       </c>
       <c r="G10" t="n">
-        <v>8.390000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="H10" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>11-08-2026</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ASAHISONG</t>
+          <t>INDIQUBE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>ASAHI SONGWON COLORS LIMITED</t>
+          <t>Indiqube Spaces Limited</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>367.9</v>
+        <v>193.17</v>
       </c>
       <c r="D11" t="n">
-        <v>338.1</v>
+        <v>164.1</v>
       </c>
       <c r="E11" t="n">
-        <v>8.800000000000001</v>
+        <v>17.7</v>
       </c>
       <c r="F11" t="n">
-        <v>66.73</v>
+        <v>60.6</v>
       </c>
       <c r="G11" t="n">
-        <v>0.34</v>
+        <v>0.25</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>11-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>INDIQUBE</t>
+          <t>ALEMBICLTD</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Indiqube Spaces Limited</t>
+          <t>Alembic Limited</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>193.17</v>
+        <v>100.14</v>
       </c>
       <c r="D12" t="n">
-        <v>164.1</v>
+        <v>91.62</v>
       </c>
       <c r="E12" t="n">
-        <v>17.7</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="F12" t="n">
-        <v>60.6</v>
+        <v>70.88</v>
       </c>
       <c r="G12" t="n">
-        <v>0.25</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="H12" t="n">
         <v>4</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
     </row>
@@ -5632,105 +5535,105 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>NRL</t>
+          <t>SINCLAIR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>NUPUR RECYCLERS LIMITED</t>
+          <t>SINCLAIRS HOTELS LIMITED</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>122</v>
+        <v>82.67</v>
       </c>
       <c r="D14" t="n">
-        <v>82.93000000000001</v>
+        <v>77.26000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>47.1</v>
+        <v>7</v>
       </c>
       <c r="F14" t="n">
-        <v>72.53</v>
+        <v>62.78</v>
       </c>
       <c r="G14" t="n">
-        <v>0.42</v>
+        <v>2.77</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SINCLAIR</t>
+          <t>UYFINCORP</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SINCLAIRS HOTELS LIMITED</t>
+          <t>U. Y. Fincorp Limited</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>82.67</v>
+        <v>19.3</v>
       </c>
       <c r="D15" t="n">
-        <v>77.26000000000001</v>
+        <v>21.01</v>
       </c>
       <c r="E15" t="n">
-        <v>7</v>
+        <v>-8.1</v>
       </c>
       <c r="F15" t="n">
-        <v>62.78</v>
+        <v>70.87</v>
       </c>
       <c r="G15" t="n">
-        <v>2.77</v>
+        <v>0.5</v>
       </c>
       <c r="H15" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>19-08-2026</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>UYFINCORP</t>
+          <t>STEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U. Y. Fincorp Limited</t>
+          <t>STEL HOLDINGS LIMITED</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19.3</v>
+        <v>601.45</v>
       </c>
       <c r="D16" t="n">
-        <v>21.01</v>
+        <v>580.77</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.1</v>
+        <v>3.6</v>
       </c>
       <c r="F16" t="n">
-        <v>70.87</v>
+        <v>64.68000000000001</v>
       </c>
       <c r="G16" t="n">
-        <v>0.5</v>
+        <v>6.04</v>
       </c>
       <c r="H16" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>19-08-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
@@ -5772,140 +5675,140 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STEL</t>
+          <t>DIAMONDYD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>STEL HOLDINGS LIMITED</t>
+          <t>Prataap Snacks Limited</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>601.45</v>
+        <v>1155.2</v>
       </c>
       <c r="D18" t="n">
-        <v>580.77</v>
+        <v>1174.34</v>
       </c>
       <c r="E18" t="n">
-        <v>3.6</v>
+        <v>-1.6</v>
       </c>
       <c r="F18" t="n">
-        <v>64.68000000000001</v>
+        <v>69.75</v>
       </c>
       <c r="G18" t="n">
-        <v>6.04</v>
+        <v>65.58</v>
       </c>
       <c r="H18" t="n">
-        <v>44</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>07-08-2026</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>DIAMONDYD</t>
+          <t>SRHHYPOLTD</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Prataap Snacks Limited</t>
+          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1155.2</v>
+        <v>498.2</v>
       </c>
       <c r="D19" t="n">
-        <v>1174.34</v>
+        <v>482.22</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.6</v>
+        <v>3.3</v>
       </c>
       <c r="F19" t="n">
-        <v>69.75</v>
+        <v>62.09</v>
       </c>
       <c r="G19" t="n">
-        <v>65.58</v>
+        <v>0.79</v>
       </c>
       <c r="H19" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>07-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SRHHYPOLTD</t>
+          <t>RGL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Sree Rayalaseema Hi-Strength Hypo Limited</t>
+          <t>Renaissance Global Limited</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>498.2</v>
+        <v>137.79</v>
       </c>
       <c r="D20" t="n">
-        <v>482.22</v>
+        <v>100.9</v>
       </c>
       <c r="E20" t="n">
-        <v>3.3</v>
+        <v>36.6</v>
       </c>
       <c r="F20" t="n">
-        <v>62.09</v>
+        <v>69.56</v>
       </c>
       <c r="G20" t="n">
-        <v>0.79</v>
+        <v>3.01</v>
       </c>
       <c r="H20" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>RGL</t>
+          <t>NRL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Renaissance Global Limited</t>
+          <t>NUPUR RECYCLERS LIMITED</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>137.79</v>
+        <v>122</v>
       </c>
       <c r="D21" t="n">
-        <v>100.9</v>
+        <v>83.06</v>
       </c>
       <c r="E21" t="n">
-        <v>36.6</v>
+        <v>46.9</v>
       </c>
       <c r="F21" t="n">
-        <v>69.56</v>
+        <v>72.53</v>
       </c>
       <c r="G21" t="n">
-        <v>3.01</v>
+        <v>0.42</v>
       </c>
       <c r="H21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
@@ -6017,70 +5920,70 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ARSSBL</t>
+          <t>THOMASCOOK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Anand Rathi Share and Stock Brokers Limited</t>
+          <t>THOMAS COOK (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>508.3</v>
+        <v>106.09</v>
       </c>
       <c r="D25" t="n">
-        <v>545.03</v>
+        <v>109.31</v>
       </c>
       <c r="E25" t="n">
-        <v>-6.7</v>
+        <v>-2.9</v>
       </c>
       <c r="F25" t="n">
-        <v>69.90000000000001</v>
+        <v>72.34</v>
       </c>
       <c r="G25" t="n">
-        <v>1.09</v>
+        <v>48.4</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>11-06-2026</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>THOMASCOOK</t>
+          <t>ARSSBL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>THOMAS COOK (INDIA) LIMITED</t>
+          <t>Anand Rathi Share and Stock Brokers Limited</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>106.09</v>
+        <v>508.3</v>
       </c>
       <c r="D26" t="n">
-        <v>109.31</v>
+        <v>545.03</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.9</v>
+        <v>-6.7</v>
       </c>
       <c r="F26" t="n">
-        <v>72.34</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="G26" t="n">
-        <v>48.4</v>
+        <v>1.09</v>
       </c>
       <c r="H26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
@@ -6157,70 +6060,70 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>VIVIANA</t>
+          <t>SILVERTUC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>VIVIANA POWER TECH LIMITED</t>
+          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>750.4</v>
+        <v>173.81</v>
       </c>
       <c r="D29" t="n">
-        <v>815.16</v>
+        <v>175.74</v>
       </c>
       <c r="E29" t="n">
-        <v>-7.9</v>
+        <v>-1.1</v>
       </c>
       <c r="F29" t="n">
-        <v>73.2</v>
+        <v>74.59</v>
       </c>
       <c r="G29" t="n">
-        <v>1.24</v>
+        <v>0.49</v>
       </c>
       <c r="H29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>29-06-2026</t>
+          <t>31-08-2026</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SILVERTUC</t>
+          <t>VIVIANA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SILVER TOUCH TECHNOLOGIES LIMITED</t>
+          <t>VIVIANA POWER TECH LIMITED</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>173.81</v>
+        <v>750.4</v>
       </c>
       <c r="D30" t="n">
-        <v>175.74</v>
+        <v>815.16</v>
       </c>
       <c r="E30" t="n">
-        <v>-1.1</v>
+        <v>-7.9</v>
       </c>
       <c r="F30" t="n">
-        <v>74.59</v>
+        <v>73.2</v>
       </c>
       <c r="G30" t="n">
-        <v>0.49</v>
+        <v>1.24</v>
       </c>
       <c r="H30" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>31-08-2026</t>
+          <t>29-06-2026</t>
         </is>
       </c>
     </row>
@@ -6297,558 +6200,523 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>EUROPRATIK</t>
+          <t>OMPOWER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Euro Pratik Sales Limited</t>
+          <t>Om Power Transmission Limited</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>260.05</v>
+        <v>171.86</v>
       </c>
       <c r="D33" t="n">
-        <v>257.65</v>
+        <v>182.69</v>
       </c>
       <c r="E33" t="n">
-        <v>0.9</v>
+        <v>-5.9</v>
       </c>
       <c r="F33" t="n">
-        <v>70.09</v>
+        <v>69.05</v>
       </c>
       <c r="G33" t="n">
-        <v>1.64</v>
+        <v>0.74</v>
       </c>
       <c r="H33" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>29-05-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>OMPOWER</t>
+          <t>VSTL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Om Power Transmission Limited</t>
+          <t>VIBHOR STEEL TUBES LIMITED</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>171.86</v>
+        <v>113.76</v>
       </c>
       <c r="D34" t="n">
-        <v>182.69</v>
+        <v>113.42</v>
       </c>
       <c r="E34" t="n">
-        <v>-5.9</v>
+        <v>0.3</v>
       </c>
       <c r="F34" t="n">
-        <v>69.05</v>
+        <v>73.48</v>
       </c>
       <c r="G34" t="n">
-        <v>0.74</v>
+        <v>0.65</v>
       </c>
       <c r="H34" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>VSTL</t>
+          <t>AJMERA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>VIBHOR STEEL TUBES LIMITED</t>
+          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>113.76</v>
+        <v>115.69</v>
       </c>
       <c r="D35" t="n">
-        <v>113.42</v>
+        <v>114.86</v>
       </c>
       <c r="E35" t="n">
-        <v>0.3</v>
+        <v>0.7</v>
       </c>
       <c r="F35" t="n">
-        <v>73.48</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="G35" t="n">
-        <v>0.65</v>
+        <v>7.36</v>
       </c>
       <c r="H35" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>04-06-2026</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AJMERA</t>
+          <t>GOKUL</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>AJMERA REALTY &amp; INFRA INDIA LIMITED</t>
+          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>115.69</v>
+        <v>41.37</v>
       </c>
       <c r="D36" t="n">
-        <v>114.86</v>
+        <v>42.65</v>
       </c>
       <c r="E36" t="n">
-        <v>0.7</v>
+        <v>-3</v>
       </c>
       <c r="F36" t="n">
-        <v>69.73999999999999</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>7.36</v>
+        <v>1.45</v>
       </c>
       <c r="H36" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>04-06-2026</t>
+          <t>01-09-2026</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>GOKUL</t>
+          <t>TRUALT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>GOKUL REFOILS AND SOLVENT LIMITED</t>
+          <t>TRUALT BIOENERGY LIMITED</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>41.37</v>
+        <v>428.85</v>
       </c>
       <c r="D37" t="n">
-        <v>42.65</v>
+        <v>474.82</v>
       </c>
       <c r="E37" t="n">
-        <v>-3</v>
+        <v>-9.699999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>71.79000000000001</v>
+        <v>70.55</v>
       </c>
       <c r="G37" t="n">
-        <v>1.45</v>
+        <v>10.22</v>
       </c>
       <c r="H37" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>01-09-2026</t>
+          <t>12-08-2026</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TRUALT</t>
+          <t>PKTEA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TRUALT BIOENERGY LIMITED</t>
+          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>428.85</v>
+        <v>728.65</v>
       </c>
       <c r="D38" t="n">
-        <v>474.82</v>
+        <v>717.77</v>
       </c>
       <c r="E38" t="n">
-        <v>-9.699999999999999</v>
+        <v>1.5</v>
       </c>
       <c r="F38" t="n">
-        <v>70.55</v>
+        <v>61.71</v>
       </c>
       <c r="G38" t="n">
-        <v>10.22</v>
+        <v>1.61</v>
       </c>
       <c r="H38" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>12-08-2026</t>
+          <t>20-08-2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>PKTEA</t>
+          <t>OBCL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>THE PERIA KARAMALAI TEA &amp; PRODUCE COMPANY LIMITED</t>
+          <t>OBCL LIMITED</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>728.65</v>
+        <v>54.77</v>
       </c>
       <c r="D39" t="n">
-        <v>717.77</v>
+        <v>53.51</v>
       </c>
       <c r="E39" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="F39" t="n">
-        <v>61.71</v>
+        <v>67.23</v>
       </c>
       <c r="G39" t="n">
-        <v>1.61</v>
+        <v>2.03</v>
       </c>
       <c r="H39" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>20-08-2026</t>
+          <t>02-09-2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>OBCL</t>
+          <t>DOLLAR</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OBCL LIMITED</t>
+          <t>DOLLAR INDUSTRIES LIMITED</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>54.77</v>
+        <v>262.35</v>
       </c>
       <c r="D40" t="n">
-        <v>53.51</v>
+        <v>269.7</v>
       </c>
       <c r="E40" t="n">
-        <v>2.4</v>
+        <v>-2.7</v>
       </c>
       <c r="F40" t="n">
-        <v>67.23</v>
+        <v>73.09</v>
       </c>
       <c r="G40" t="n">
-        <v>2.03</v>
+        <v>1.48</v>
       </c>
       <c r="H40" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>02-09-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>DOLLAR</t>
+          <t>BMWVENTLTD</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>DOLLAR INDUSTRIES LIMITED</t>
+          <t>BMW VENTURES LIMITED</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>262.35</v>
+        <v>55.23</v>
       </c>
       <c r="D41" t="n">
-        <v>269.7</v>
+        <v>60.15</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.7</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="F41" t="n">
-        <v>73.09</v>
+        <v>73.01000000000001</v>
       </c>
       <c r="G41" t="n">
-        <v>1.48</v>
+        <v>0.9</v>
       </c>
       <c r="H41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>06-08-2026</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>BMWVENTLTD</t>
+          <t>GRMOVER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BMW VENTURES LIMITED</t>
+          <t>GRM OVERSEAS LIMITED</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>55.23</v>
+        <v>86.03</v>
       </c>
       <c r="D42" t="n">
-        <v>60.15</v>
+        <v>95.54000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>-8.199999999999999</v>
+        <v>-10</v>
       </c>
       <c r="F42" t="n">
-        <v>73.01000000000001</v>
+        <v>71.72</v>
       </c>
       <c r="G42" t="n">
-        <v>0.9</v>
+        <v>10.87</v>
       </c>
       <c r="H42" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>06-08-2026</t>
+          <t>24-06-2026</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>GRMOVER</t>
+          <t>LAOPALA</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>GRM OVERSEAS LIMITED</t>
+          <t>LA OPALA RG LIMITED</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>86.03</v>
+        <v>171.87</v>
       </c>
       <c r="D43" t="n">
-        <v>95.54000000000001</v>
+        <v>173.91</v>
       </c>
       <c r="E43" t="n">
-        <v>-10</v>
+        <v>-1.2</v>
       </c>
       <c r="F43" t="n">
-        <v>71.72</v>
+        <v>65.64</v>
       </c>
       <c r="G43" t="n">
-        <v>10.87</v>
+        <v>2.61</v>
       </c>
       <c r="H43" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>24-06-2026</t>
+          <t>08-06-2026</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LAOPALA</t>
+          <t>MBEL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>LA OPALA RG LIMITED</t>
+          <t>M &amp; B Engineering Limited</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>171.87</v>
+        <v>266.1</v>
       </c>
       <c r="D44" t="n">
-        <v>173.91</v>
+        <v>292.28</v>
       </c>
       <c r="E44" t="n">
-        <v>-1.2</v>
+        <v>-9</v>
       </c>
       <c r="F44" t="n">
-        <v>65.64</v>
+        <v>70.45</v>
       </c>
       <c r="G44" t="n">
-        <v>2.61</v>
+        <v>1.29</v>
       </c>
       <c r="H44" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>08-06-2026</t>
+          <t>16-06-2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>MBEL</t>
+          <t>TIGERLOGS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>M &amp; B Engineering Limited</t>
+          <t>Tiger Logistics (India) Limited</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>266.1</v>
+        <v>28.25</v>
       </c>
       <c r="D45" t="n">
-        <v>292.28</v>
+        <v>34.54</v>
       </c>
       <c r="E45" t="n">
-        <v>-9</v>
+        <v>-18.2</v>
       </c>
       <c r="F45" t="n">
-        <v>70.45</v>
+        <v>61.81</v>
       </c>
       <c r="G45" t="n">
-        <v>1.29</v>
+        <v>0.88</v>
       </c>
       <c r="H45" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>16-06-2026</t>
+          <t>24-08-2026</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TIGERLOGS</t>
+          <t>HEXAGON</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Tiger Logistics (India) Limited</t>
+          <t>HEXAGON NUTRITION LIMITED</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>28.25</v>
+        <v>66.14</v>
       </c>
       <c r="D46" t="n">
-        <v>34.54</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>-18.2</v>
+        <v>3.3</v>
       </c>
       <c r="F46" t="n">
-        <v>61.81</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>0.88</v>
+        <v>0.31</v>
       </c>
       <c r="H46" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>24-08-2026</t>
+          <t>17-08-2026</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>HEXAGON</t>
+          <t>WCIL</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HEXAGON NUTRITION LIMITED</t>
+          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>66.14</v>
+        <v>84.28</v>
       </c>
       <c r="D47" t="n">
-        <v>64.04000000000001</v>
+        <v>100.33</v>
       </c>
       <c r="E47" t="n">
-        <v>3.3</v>
+        <v>-16</v>
       </c>
       <c r="F47" t="n">
-        <v>64.29000000000001</v>
+        <v>71.89</v>
       </c>
       <c r="G47" t="n">
-        <v>0.31</v>
+        <v>0.63</v>
       </c>
       <c r="H47" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I47" t="inlineStr">
-        <is>
-          <t>17-08-2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>WCIL</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>WESTERN CARRIERS (INDIA) LIMITED</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>84.28</v>
-      </c>
-      <c r="D48" t="n">
-        <v>100.33</v>
-      </c>
-      <c r="E48" t="n">
-        <v>-16</v>
-      </c>
-      <c r="F48" t="n">
-        <v>71.89</v>
-      </c>
-      <c r="G48" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="H48" t="n">
-        <v>5</v>
-      </c>
-      <c r="I48" t="inlineStr">
         <is>
           <t>30-06-2026</t>
         </is>
@@ -6887,7 +6755,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3">
@@ -6977,7 +6845,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
